--- a/tests/regression_artifacts/downloads/email_03152025_ASHIONNOVA/current/140070017.xlsx
+++ b/tests/regression_artifacts/downloads/email_03152025_ASHIONNOVA/current/140070017.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Invoice Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Invoice Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -739,19 +739,19 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Apparel; not knitted or crocheted</t>
+          <t>OTHER TOYS</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>62034290</t>
+          <t>95030090</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>62034290</t>
+          <t>95030090</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -831,7 +831,7 @@
       <c r="AJ2" s="2" t="n"/>
       <c r="AK2" s="2" t="inlineStr">
         <is>
-          <t>62034290</t>
+          <t>95030090</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       <c r="E3" s="4" t="n"/>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>62034290</t>
+          <t>95030090</t>
         </is>
       </c>
       <c r="G3" s="4" t="n"/>
@@ -917,19 +917,19 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Singlets and other vests</t>
+          <t>PRODUCTS</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>61091020</t>
+          <t>00000000</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>61091020</t>
+          <t>00000000</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -981,7 +981,7 @@
       <c r="AJ4" s="2" t="n"/>
       <c r="AK4" s="2" t="inlineStr">
         <is>
-          <t>61091020</t>
+          <t>00000000</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       <c r="E5" s="4" t="n"/>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>61091020</t>
+          <t>00000000</t>
         </is>
       </c>
       <c r="G5" s="4" t="n"/>
@@ -1060,7 +1060,7 @@
       <c r="E6" s="4" t="n"/>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>61091020</t>
+          <t>00000000</t>
         </is>
       </c>
       <c r="G6" s="4" t="n"/>
@@ -1833,7 +1833,7 @@
       <c r="I26" s="13" t="n"/>
       <c r="J26" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  └ 61091020: 20% CET (50% of value)</t>
+          <t xml:space="preserve">  └ 00000000: 20% CET (50% of value)</t>
         </is>
       </c>
       <c r="K26" s="13" t="n"/>
@@ -1878,7 +1878,7 @@
       <c r="I27" s="13" t="n"/>
       <c r="J27" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  └ 62034290: 20% CET (50% of value)</t>
+          <t xml:space="preserve">  └ 95030090: 20% CET (50% of value)</t>
         </is>
       </c>
       <c r="K27" s="13" t="n"/>
